--- a/docs/回答評価シート.xlsx
+++ b/docs/回答評価シート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kokoh\CTF\CTF_HTML\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3414749F-B022-4208-81F8-1DF0E38EA274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E931BD5-FB0B-4A83-8BD5-5DF8827AD4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{F05016BD-9C70-4A26-8675-335515EFD43C}"/>
   </bookViews>
@@ -1437,13 +1437,34 @@
         <f>_xlfn.XLOOKUP(A7,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ホヌ柄の飛行機ってどこの航空会社？</v>
       </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
       <c r="K7">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L7" t="e">
+        <v>14</v>
+      </c>
+      <c r="L7">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -1458,13 +1479,34 @@
         <f>_xlfn.XLOOKUP(A8,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ハワイの空港の公式WiFiの名前なに</v>
       </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
       <c r="K8">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L8" t="e">
+        <v>23</v>
+      </c>
+      <c r="L8">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -1479,13 +1521,34 @@
         <f>_xlfn.XLOOKUP(A9,質問シート!A:A,質問シート!C:C,"")</f>
         <v>空港のWiFiのSSIDって簡単にわかる？</v>
       </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
       <c r="K9">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L9" t="e">
+        <v>25</v>
+      </c>
+      <c r="L9">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -1500,13 +1563,34 @@
         <f>_xlfn.XLOOKUP(A10,質問シート!A:A,質問シート!C:C,"")</f>
         <v>飛行機の便名と日付って結びつけられる？</v>
       </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
       <c r="K10">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L10" t="e">
+        <v>26</v>
+      </c>
+      <c r="L10">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
@@ -1521,13 +1605,34 @@
         <f>_xlfn.XLOOKUP(A11,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ギリシャ神話で医療の神って誰</v>
       </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
       <c r="K11">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L11" t="e">
+        <v>22</v>
+      </c>
+      <c r="L11">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.1428571428571428</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
@@ -1542,13 +1647,34 @@
         <f>_xlfn.XLOOKUP(A12,質問シート!A:A,質問シート!C:C,"")</f>
         <v>杖に蛇が巻き付いてるシンボルって何の神</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
       <c r="K12">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L12" t="e">
+        <v>21</v>
+      </c>
+      <c r="L12">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -1563,13 +1689,34 @@
         <f>_xlfn.XLOOKUP(A13,質問シート!A:A,質問シート!C:C,"")</f>
         <v>創立100年くらいの有名な日本の私立大学は？</v>
       </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>5</v>
+      </c>
       <c r="K13">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L13" t="e">
+        <v>27</v>
+      </c>
+      <c r="L13">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
@@ -1584,13 +1731,34 @@
         <f>_xlfn.XLOOKUP(A14,質問シート!A:A,質問シート!C:C,"")</f>
         <v>慶應義塾を作った人って誰</v>
       </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
       <c r="K14">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L14" t="e">
+        <v>17</v>
+      </c>
+      <c r="L14">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.4285714285714284</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
@@ -1605,13 +1773,34 @@
         <f>_xlfn.XLOOKUP(A15,質問シート!A:A,質問シート!C:C,"")</f>
         <v>google画像検索のやり方</v>
       </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
       <c r="K15">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L15" t="e">
+        <v>23</v>
+      </c>
+      <c r="L15">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
@@ -1626,13 +1815,34 @@
         <f>_xlfn.XLOOKUP(A16,質問シート!A:A,質問シート!C:C,"")</f>
         <v>座標から事件を調べたい</v>
       </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
       <c r="K16">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L16" t="e">
+        <v>24</v>
+      </c>
+      <c r="L16">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
@@ -1647,13 +1857,34 @@
         <f>_xlfn.XLOOKUP(A17,質問シート!A:A,質問シート!C:C,"")</f>
         <v>60.8841988,101.8857172 で何が起きた</v>
       </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
       <c r="K17">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L17" t="e">
+        <v>18</v>
+      </c>
+      <c r="L17">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.5714285714285716</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
@@ -1668,13 +1899,34 @@
         <f>_xlfn.XLOOKUP(A18,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ツングースカ大爆発ってなに</v>
       </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
       <c r="K18">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L18" t="e">
+        <v>18</v>
+      </c>
+      <c r="L18">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.5714285714285716</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
@@ -1689,13 +1941,34 @@
         <f>_xlfn.XLOOKUP(A19,質問シート!A:A,質問シート!C:C,"")</f>
         <v>特許を調べるサイト教えて</v>
       </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>5</v>
+      </c>
       <c r="K19">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L19" t="e">
+        <v>31</v>
+      </c>
+      <c r="L19">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
@@ -1710,13 +1983,34 @@
         <f>_xlfn.XLOOKUP(A20,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Google Patentsの使い方</v>
       </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
       <c r="K20">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L20" t="e">
+        <v>23</v>
+      </c>
+      <c r="L20">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
@@ -1731,13 +2025,34 @@
         <f>_xlfn.XLOOKUP(A21,質問シート!A:A,質問シート!C:C,"")</f>
         <v>画像から場所を特定するために、最初に確認すべき情報は？</v>
       </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
       <c r="K21">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L21" t="e">
+        <v>26</v>
+      </c>
+      <c r="L21">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
@@ -1752,13 +2067,34 @@
         <f>_xlfn.XLOOKUP(A22,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SNSアカウント同士の関連性を調べる一般的な方法は？</v>
       </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
       <c r="K22">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L22" t="e">
+        <v>20</v>
+      </c>
+      <c r="L22">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.8571428571428572</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
@@ -1773,13 +2109,34 @@
         <f>_xlfn.XLOOKUP(A23,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ドメインの登録情報を確認するにはどんな手法がある？</v>
       </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
       <c r="K23">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L23" t="e">
+        <v>26</v>
+      </c>
+      <c r="L23">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
@@ -1794,13 +2151,34 @@
         <f>_xlfn.XLOOKUP(A24,質問シート!A:A,質問シート!C:C,"")</f>
         <v>EXIF情報から取得できる代表的なデータは？</v>
       </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
+      </c>
       <c r="K24">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L24" t="e">
+        <v>33</v>
+      </c>
+      <c r="L24">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.4">
@@ -1815,13 +2193,34 @@
         <f>_xlfn.XLOOKUP(A25,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Wayback Machineはどんな用途で使われる？</v>
       </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>5</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
       <c r="K25">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L25" t="e">
+        <v>29</v>
+      </c>
+      <c r="L25">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
@@ -1836,13 +2235,34 @@
         <f>_xlfn.XLOOKUP(A26,質問シート!A:A,質問シート!C:C,"")</f>
         <v>GitHubの公開リポジトリから秘密情報を探す時の観点は？</v>
       </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
       <c r="K26">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L26" t="e">
+        <v>26</v>
+      </c>
+      <c r="L26">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
@@ -1857,13 +2277,34 @@
         <f>_xlfn.XLOOKUP(A27,質問シート!A:A,質問シート!C:C,"")</f>
         <v>電話番号から得られるOSINT情報には何がある？</v>
       </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
       <c r="K27">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L27" t="e">
+        <v>13</v>
+      </c>
+      <c r="L27">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>1.8571428571428572</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.4">
@@ -1878,13 +2319,34 @@
         <f>_xlfn.XLOOKUP(A28,質問シート!A:A,質問シート!C:C,"")</f>
         <v>DNSレコードを調査すると何がわかる？</v>
       </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>5</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
       <c r="K28">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L28" t="e">
+        <v>28</v>
+      </c>
+      <c r="L28">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.4">
@@ -1899,13 +2361,34 @@
         <f>_xlfn.XLOOKUP(A29,質問シート!A:A,質問シート!C:C,"")</f>
         <v>リバースイメージサーチの代表的な使い方を教えて。</v>
       </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>5</v>
+      </c>
       <c r="K29">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L29" t="e">
+        <v>31</v>
+      </c>
+      <c r="L29">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.4">
@@ -1920,13 +2403,34 @@
         <f>_xlfn.XLOOKUP(A30,質問シート!A:A,質問シート!C:C,"")</f>
         <v>OSINTで得た情報の信頼性を検証する方法は？</v>
       </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30">
+        <v>4</v>
+      </c>
       <c r="K30">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L30" t="e">
+        <v>29</v>
+      </c>
+      <c r="L30">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
@@ -1941,13 +2445,34 @@
         <f>_xlfn.XLOOKUP(A31,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Webカテゴリで最初に試すべき脆弱性チェック項目を優先度順に挙げてください。</v>
       </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>4</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31">
+        <v>5</v>
+      </c>
       <c r="K31">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L31" t="e">
+        <v>25</v>
+      </c>
+      <c r="L31">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.4">
@@ -1962,13 +2487,34 @@
         <f>_xlfn.XLOOKUP(A32,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SQL Injectionの基本原理を、危険な例と安全な対策をセットで説明してください。</v>
       </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>4</v>
+      </c>
+      <c r="I32">
+        <v>5</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
       <c r="K32">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L32" t="e">
+        <v>27</v>
+      </c>
+      <c r="L32">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.4">
@@ -1983,13 +2529,34 @@
         <f>_xlfn.XLOOKUP(A33,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XSS（反射型・保存型・DOM型）の違いを簡潔に比較してください。</v>
       </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+      <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
       <c r="K33">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L33" t="e">
+        <v>26</v>
+      </c>
+      <c r="L33">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.4">
@@ -2004,13 +2571,34 @@
         <f>_xlfn.XLOOKUP(A34,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SSRFが成立する条件と、実運用での防御策を説明してください。</v>
       </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
       <c r="K34">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L34" t="e">
+        <v>23</v>
+      </c>
+      <c r="L34">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.4">
@@ -2025,13 +2613,34 @@
         <f>_xlfn.XLOOKUP(A35,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CTFのWeb問題で「ソースを見る」が有効な理由を具体例つきで説明してください。</v>
       </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>5</v>
+      </c>
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
       <c r="K35">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L35" t="e">
+        <v>20</v>
+      </c>
+      <c r="L35">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.8571428571428572</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.4">
@@ -2046,13 +2655,34 @@
         <f>_xlfn.XLOOKUP(A36,質問シート!A:A,質問シート!C:C,"")</f>
         <v>HTMLのコメントってどこから見れる?</v>
       </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
       <c r="K36">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L36" t="e">
+        <v>20</v>
+      </c>
+      <c r="L36">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.8571428571428572</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
@@ -2067,13 +2697,34 @@
         <f>_xlfn.XLOOKUP(A37,質問シート!A:A,質問シート!C:C,"")</f>
         <v>F12を押すと何ができるの</v>
       </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <v>5</v>
+      </c>
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
       <c r="K37">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L37" t="e">
+        <v>24</v>
+      </c>
+      <c r="L37">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
@@ -2088,13 +2739,34 @@
         <f>_xlfn.XLOOKUP(A38,質問シート!A:A,質問シート!C:C,"")</f>
         <v>IDORって何の略</v>
       </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>4</v>
+      </c>
       <c r="K38">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L38" t="e">
+        <v>16</v>
+      </c>
+      <c r="L38">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.2857142857142856</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
@@ -2109,13 +2781,34 @@
         <f>_xlfn.XLOOKUP(A39,質問シート!A:A,質問シート!C:C,"")</f>
         <v>robots.txtはどんな目的で使われる？</v>
       </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="H39">
+        <v>5</v>
+      </c>
+      <c r="I39">
+        <v>5</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
       <c r="K39">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L39" t="e">
+        <v>29</v>
+      </c>
+      <c r="L39">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
@@ -2130,13 +2823,34 @@
         <f>_xlfn.XLOOKUP(A40,質問シート!A:A,質問シート!C:C,"")</f>
         <v>robots.txtに書かれてる場所って入っていいの?</v>
       </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>4</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
       <c r="K40">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L40" t="e">
+        <v>18</v>
+      </c>
+      <c r="L40">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.5714285714285716</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
@@ -2151,13 +2865,34 @@
         <f>_xlfn.XLOOKUP(A41,質問シート!A:A,質問シート!C:C,"")</f>
         <v>URLのid=2を1に変えたら何が起きる</v>
       </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>3</v>
+      </c>
       <c r="K41">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L41" t="e">
+        <v>24</v>
+      </c>
+      <c r="L41">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.4">
@@ -2172,13 +2907,34 @@
         <f>_xlfn.XLOOKUP(A42,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SQLインジェクションの基本的な仕組みを説明して。</v>
       </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42">
+        <v>4</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>3</v>
+      </c>
       <c r="K42">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L42" t="e">
+        <v>28</v>
+      </c>
+      <c r="L42">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.4">
@@ -2193,13 +2949,34 @@
         <f>_xlfn.XLOOKUP(A43,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XSSにはどんな種類がある？</v>
       </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>4</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
       <c r="K43">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L43" t="e">
+        <v>27</v>
+      </c>
+      <c r="L43">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.4">
@@ -2214,13 +2991,34 @@
         <f>_xlfn.XLOOKUP(A44,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CookieとSessionの違いは？</v>
       </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
       <c r="K44">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L44" t="e">
+        <v>32</v>
+      </c>
+      <c r="L44">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.4">
@@ -2235,13 +3033,34 @@
         <f>_xlfn.XLOOKUP(A45,質問シート!A:A,質問シート!C:C,"")</f>
         <v>HTTPレスポンスコード403と404の違いは？</v>
       </c>
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
       <c r="K45">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L45" t="e">
+        <v>31</v>
+      </c>
+      <c r="L45">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
@@ -2256,13 +3075,34 @@
         <f>_xlfn.XLOOKUP(A46,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Burp Suiteは何に使うツール？</v>
       </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>5</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46">
+        <v>3</v>
+      </c>
       <c r="K46">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L46" t="e">
+        <v>28</v>
+      </c>
+      <c r="L46">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.4">
@@ -2277,13 +3117,34 @@
         <f>_xlfn.XLOOKUP(A47,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CSRF攻撃はどのように成立する？</v>
       </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
       <c r="K47">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L47" t="e">
+        <v>25</v>
+      </c>
+      <c r="L47">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.4">
@@ -2298,13 +3159,34 @@
         <f>_xlfn.XLOOKUP(A48,質問シート!A:A,質問シート!C:C,"")</f>
         <v>JWTの構造を説明して。</v>
       </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48">
+        <v>5</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
       <c r="K48">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L48" t="e">
+        <v>28</v>
+      </c>
+      <c r="L48">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.4">
@@ -2319,13 +3201,34 @@
         <f>_xlfn.XLOOKUP(A49,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ディレクトリトラバーサルとは？</v>
       </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+      <c r="J49">
+        <v>5</v>
+      </c>
       <c r="K49">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L49" t="e">
+        <v>30</v>
+      </c>
+      <c r="L49">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.4">
@@ -2340,13 +3243,34 @@
         <f>_xlfn.XLOOKUP(A50,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Webアプリのログインフォームを調査するときの一般的な観点は？</v>
       </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50">
+        <v>4</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
       <c r="K50">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L50" t="e">
+        <v>25</v>
+      </c>
+      <c r="L50">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.4">
@@ -2361,13 +3285,34 @@
         <f>_xlfn.XLOOKUP(A51,質問シート!A:A,質問シート!C:C,"")</f>
         <v>暗号化とハッシュ化の違いを、CTFでの使い分け例つきで説明してください。</v>
       </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="H51">
+        <v>4</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
+      </c>
+      <c r="J51">
+        <v>3</v>
+      </c>
       <c r="K51">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L51" t="e">
+        <v>21</v>
+      </c>
+      <c r="L51">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.4">
@@ -2382,13 +3327,34 @@
         <f>_xlfn.XLOOKUP(A52,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Caesar暗号とVigenere暗号の違いを、解読の観点で比較してください。</v>
       </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52">
+        <v>4</v>
+      </c>
+      <c r="J52">
+        <v>4</v>
+      </c>
       <c r="K52">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L52" t="e">
+        <v>23</v>
+      </c>
+      <c r="L52">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.4">
@@ -2403,13 +3369,34 @@
         <f>_xlfn.XLOOKUP(A53,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64は暗号ですか？誤解されやすい理由も含めて説明してください。</v>
       </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>5</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>4</v>
+      </c>
       <c r="K53">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L53" t="e">
+        <v>24</v>
+      </c>
+      <c r="L53">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.4">
@@ -2424,13 +3411,34 @@
         <f>_xlfn.XLOOKUP(A54,質問シート!A:A,質問シート!C:C,"")</f>
         <v>RSAの公開鍵・秘密鍵の役割を、数学が苦手な人向けに説明してください。</v>
       </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="H54">
+        <v>5</v>
+      </c>
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
       <c r="K54">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L54" t="e">
+        <v>24</v>
+      </c>
+      <c r="L54">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.4">
@@ -2445,13 +3453,34 @@
         <f>_xlfn.XLOOKUP(A55,質問シート!A:A,質問シート!C:C,"")</f>
         <v>暗号問題で「鍵長が短い」と何が起きるか、攻撃手法とあわせて説明してください。</v>
       </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
       <c r="K55">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L55" t="e">
+        <v>21</v>
+      </c>
+      <c r="L55">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.4">
@@ -2466,13 +3495,34 @@
         <f>_xlfn.XLOOKUP(A56,質問シート!A:A,質問シート!C:C,"")</f>
         <v>シーザー暗号ってROT13とどう違うの</v>
       </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>3</v>
+      </c>
+      <c r="H56">
+        <v>5</v>
+      </c>
+      <c r="I56">
+        <v>5</v>
+      </c>
+      <c r="J56">
+        <v>4</v>
+      </c>
       <c r="K56">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L56" t="e">
+        <v>24</v>
+      </c>
+      <c r="L56">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.4">
@@ -2487,13 +3537,34 @@
         <f>_xlfn.XLOOKUP(A57,質問シート!A:A,質問シート!C:C,"")</f>
         <v>数字をアルファベットに置き換える暗号って何ていう</v>
       </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="H57">
+        <v>5</v>
+      </c>
+      <c r="I57">
+        <v>4</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
       <c r="K57">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L57" t="e">
+        <v>16</v>
+      </c>
+      <c r="L57">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.2857142857142856</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.4">
@@ -2508,13 +3579,34 @@
         <f>_xlfn.XLOOKUP(A58,質問シート!A:A,質問シート!C:C,"")</f>
         <v>A1Z26方式って聞いたことある？</v>
       </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>4</v>
+      </c>
+      <c r="H58">
+        <v>5</v>
+      </c>
+      <c r="I58">
+        <v>5</v>
+      </c>
+      <c r="J58">
+        <v>5</v>
+      </c>
       <c r="K58">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L58" t="e">
+        <v>28</v>
+      </c>
+      <c r="L58">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.4">
@@ -2529,13 +3621,34 @@
         <f>_xlfn.XLOOKUP(A59,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64って何バイト単位でエンコードするの</v>
       </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>5</v>
+      </c>
+      <c r="I59">
+        <v>4</v>
+      </c>
+      <c r="J59">
+        <v>3</v>
+      </c>
       <c r="K59">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L59" t="e">
+        <v>18</v>
+      </c>
+      <c r="L59">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.5714285714285716</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.4">
@@ -2550,13 +3663,34 @@
         <f>_xlfn.XLOOKUP(A60,質問シート!A:A,質問シート!C:C,"")</f>
         <v>換字式暗号を自動で解いてくれるサイトある？</v>
       </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60">
+        <v>5</v>
+      </c>
+      <c r="J60">
+        <v>3</v>
+      </c>
       <c r="K60">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L60" t="e">
+        <v>27</v>
+      </c>
+      <c r="L60">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.4">
@@ -2571,13 +3705,34 @@
         <f>_xlfn.XLOOKUP(A61,質問シート!A:A,質問シート!C:C,"")</f>
         <v>quipqiupってどう使うの</v>
       </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>5</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>3</v>
+      </c>
       <c r="K61">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L61" t="e">
+        <v>14</v>
+      </c>
+      <c r="L61">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.4">
@@ -2592,13 +3747,34 @@
         <f>_xlfn.XLOOKUP(A62,質問シート!A:A,質問シート!C:C,"")</f>
         <v>PDFのパスワードを解析する方法</v>
       </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>3</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+      <c r="I62">
+        <v>3</v>
+      </c>
+      <c r="J62">
+        <v>4</v>
+      </c>
       <c r="K62">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L62" t="e">
+        <v>20</v>
+      </c>
+      <c r="L62">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.8571428571428572</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.4">
@@ -2613,13 +3789,34 @@
         <f>_xlfn.XLOOKUP(A63,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ROT26で解読すればいいんですよね？</v>
       </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>5</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
       <c r="K63">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L63" t="e">
+        <v>17</v>
+      </c>
+      <c r="L63">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.4285714285714284</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.4">
@@ -2634,13 +3831,34 @@
         <f>_xlfn.XLOOKUP(A64,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64って暗号だよね？</v>
       </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>4</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64">
+        <v>5</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
+      </c>
       <c r="K64">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L64" t="e">
+        <v>31</v>
+      </c>
+      <c r="L64">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.4">
@@ -2655,13 +3873,34 @@
         <f>_xlfn.XLOOKUP(A65,質問シート!A:A,質問シート!C:C,"")</f>
         <v>モールス信号って数字だけしか使えないの？</v>
       </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>5</v>
+      </c>
+      <c r="I65">
+        <v>5</v>
+      </c>
+      <c r="J65">
+        <v>4</v>
+      </c>
       <c r="K65">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L65" t="e">
+        <v>22</v>
+      </c>
+      <c r="L65">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.1428571428571428</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.4">
@@ -2676,13 +3915,34 @@
         <f>_xlfn.XLOOKUP(A66,質問シート!A:A,質問シート!C:C,"")</f>
         <v>john the ripperってウイルス対策ソフトでしょ？</v>
       </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>4</v>
+      </c>
+      <c r="F66">
+        <v>4</v>
+      </c>
+      <c r="G66">
+        <v>4</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66">
+        <v>4</v>
+      </c>
+      <c r="J66">
+        <v>5</v>
+      </c>
       <c r="K66">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L66" t="e">
+        <v>30</v>
+      </c>
+      <c r="L66">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.4">
@@ -2697,13 +3957,34 @@
         <f>_xlfn.XLOOKUP(A67,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ROT13とBase64って何が違うの</v>
       </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>3</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>5</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
       <c r="K67">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L67" t="e">
+        <v>24</v>
+      </c>
+      <c r="L67">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.4">
@@ -2718,13 +3999,34 @@
         <f>_xlfn.XLOOKUP(A68,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ステガノグラフィと暗号化って同じ？</v>
       </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>4</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68">
+        <v>4</v>
+      </c>
+      <c r="H68">
+        <v>5</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
       <c r="K68">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L68" t="e">
+        <v>30</v>
+      </c>
+      <c r="L68">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.4">
@@ -2739,13 +4041,34 @@
         <f>_xlfn.XLOOKUP(A69,質問シート!A:A,質問シート!C:C,"")</f>
         <v>シーザー暗号の復号方法を説明して。</v>
       </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>4</v>
+      </c>
+      <c r="J69">
+        <v>5</v>
+      </c>
       <c r="K69">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L69" t="e">
+        <v>20</v>
+      </c>
+      <c r="L69">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.8571428571428572</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.4">
@@ -2760,13 +4083,34 @@
         <f>_xlfn.XLOOKUP(A70,質問シート!A:A,質問シート!C:C,"")</f>
         <v>共通鍵暗号と公開鍵暗号の違いは？</v>
       </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70">
+        <v>4</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
+        <v>3</v>
+      </c>
       <c r="K70">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L70" t="e">
+        <v>26</v>
+      </c>
+      <c r="L70">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.4">
@@ -2781,13 +4125,34 @@
         <f>_xlfn.XLOOKUP(A71,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64は暗号なのかエンコードなのか説明して。</v>
       </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>5</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
       <c r="K71">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L71" t="e">
+        <v>27</v>
+      </c>
+      <c r="L71">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.4">
@@ -2802,13 +4167,34 @@
         <f>_xlfn.XLOOKUP(A72,質問シート!A:A,質問シート!C:C,"")</f>
         <v>RSA暗号の基本的な仕組みを教えて。</v>
       </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+      <c r="H72">
+        <v>5</v>
+      </c>
+      <c r="I72">
+        <v>5</v>
+      </c>
+      <c r="J72">
+        <v>3</v>
+      </c>
       <c r="K72">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L72" t="e">
+        <v>23</v>
+      </c>
+      <c r="L72">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.4">
@@ -2823,13 +4209,34 @@
         <f>_xlfn.XLOOKUP(A73,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ハッシュ関数の用途は？</v>
       </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73">
+        <v>4</v>
+      </c>
+      <c r="F73">
+        <v>3</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>5</v>
+      </c>
+      <c r="I73">
+        <v>5</v>
+      </c>
+      <c r="J73">
+        <v>3</v>
+      </c>
       <c r="K73">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L73" t="e">
+        <v>24</v>
+      </c>
+      <c r="L73">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.4">
@@ -2844,13 +4251,34 @@
         <f>_xlfn.XLOOKUP(A74,質問シート!A:A,質問シート!C:C,"")</f>
         <v>AESがよく使われる理由は？</v>
       </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>3</v>
+      </c>
+      <c r="H74">
+        <v>5</v>
+      </c>
+      <c r="I74">
+        <v>5</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
       <c r="K74">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L74" t="e">
+        <v>25</v>
+      </c>
+      <c r="L74">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.4">
@@ -2865,13 +4293,34 @@
         <f>_xlfn.XLOOKUP(A75,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XOR暗号の特徴を説明して。</v>
       </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75">
+        <v>5</v>
+      </c>
+      <c r="I75">
+        <v>5</v>
+      </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
       <c r="K75">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L75" t="e">
+        <v>25</v>
+      </c>
+      <c r="L75">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.4">
@@ -2886,13 +4335,34 @@
         <f>_xlfn.XLOOKUP(A76,質問シート!A:A,質問シート!C:C,"")</f>
         <v>頻度分析が有効な暗号方式の例を挙げて。</v>
       </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+      <c r="H76">
+        <v>5</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
       <c r="K76">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L76" t="e">
+        <v>28</v>
+      </c>
+      <c r="L76">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.4">
@@ -2907,13 +4377,34 @@
         <f>_xlfn.XLOOKUP(A77,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ソルト付きハッシュの目的は？</v>
       </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>3</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>3</v>
+      </c>
+      <c r="H77">
+        <v>5</v>
+      </c>
+      <c r="I77">
+        <v>5</v>
+      </c>
+      <c r="J77">
+        <v>5</v>
+      </c>
       <c r="K77">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L77" t="e">
+        <v>26</v>
+      </c>
+      <c r="L77">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.4">
@@ -2928,13 +4419,34 @@
         <f>_xlfn.XLOOKUP(A78,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Vigenère暗号の解読で使われる代表的な手法は？</v>
       </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>5</v>
+      </c>
+      <c r="I78">
+        <v>4</v>
+      </c>
+      <c r="J78">
+        <v>5</v>
+      </c>
       <c r="K78">
         <f>SUM(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L78" t="e">
+        <v>19</v>
+      </c>
+      <c r="L78">
         <f>AVERAGE(テーブル1[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.7142857142857144</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.4">
@@ -4977,6 +6489,28 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="D2:J175">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2.5"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L175">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -5277,13 +6811,34 @@
         <f>_xlfn.XLOOKUP(A7,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ホヌ柄の飛行機ってどこの航空会社？</v>
       </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
       <c r="K7">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L7" t="e">
+        <v>23</v>
+      </c>
+      <c r="L7">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -5298,13 +6853,34 @@
         <f>_xlfn.XLOOKUP(A8,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ハワイの空港の公式WiFiの名前なに</v>
       </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
       <c r="K8">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L8" t="e">
+        <v>29</v>
+      </c>
+      <c r="L8">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -5319,13 +6895,34 @@
         <f>_xlfn.XLOOKUP(A9,質問シート!A:A,質問シート!C:C,"")</f>
         <v>空港のWiFiのSSIDって簡単にわかる？</v>
       </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
       <c r="K9">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L9" t="e">
+        <v>30</v>
+      </c>
+      <c r="L9">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -5340,13 +6937,34 @@
         <f>_xlfn.XLOOKUP(A10,質問シート!A:A,質問シート!C:C,"")</f>
         <v>飛行機の便名と日付って結びつけられる？</v>
       </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
       <c r="K10">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L10" t="e">
+        <v>33</v>
+      </c>
+      <c r="L10">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
@@ -5361,13 +6979,34 @@
         <f>_xlfn.XLOOKUP(A11,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ギリシャ神話で医療の神って誰</v>
       </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
       <c r="K11">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L11" t="e">
+        <v>32</v>
+      </c>
+      <c r="L11">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
@@ -5382,13 +7021,34 @@
         <f>_xlfn.XLOOKUP(A12,質問シート!A:A,質問シート!C:C,"")</f>
         <v>杖に蛇が巻き付いてるシンボルって何の神</v>
       </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
       <c r="K12">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L12" t="e">
+        <v>25</v>
+      </c>
+      <c r="L12">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -5403,13 +7063,34 @@
         <f>_xlfn.XLOOKUP(A13,質問シート!A:A,質問シート!C:C,"")</f>
         <v>創立100年くらいの有名な日本の私立大学は？</v>
       </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
       <c r="K13">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L13" t="e">
+        <v>24</v>
+      </c>
+      <c r="L13">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
@@ -5424,13 +7105,34 @@
         <f>_xlfn.XLOOKUP(A14,質問シート!A:A,質問シート!C:C,"")</f>
         <v>慶應義塾を作った人って誰</v>
       </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
       <c r="K14">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L14" t="e">
+        <v>26</v>
+      </c>
+      <c r="L14">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
@@ -5445,13 +7147,34 @@
         <f>_xlfn.XLOOKUP(A15,質問シート!A:A,質問シート!C:C,"")</f>
         <v>google画像検索のやり方</v>
       </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
       <c r="K15">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L15" t="e">
+        <v>31</v>
+      </c>
+      <c r="L15">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
@@ -5466,13 +7189,34 @@
         <f>_xlfn.XLOOKUP(A16,質問シート!A:A,質問シート!C:C,"")</f>
         <v>座標から事件を調べたい</v>
       </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
       <c r="K16">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L16" t="e">
+        <v>27</v>
+      </c>
+      <c r="L16">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
@@ -5487,13 +7231,34 @@
         <f>_xlfn.XLOOKUP(A17,質問シート!A:A,質問シート!C:C,"")</f>
         <v>60.8841988,101.8857172 で何が起きた</v>
       </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
       <c r="K17">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L17" t="e">
+        <v>27</v>
+      </c>
+      <c r="L17">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
@@ -5508,13 +7273,34 @@
         <f>_xlfn.XLOOKUP(A18,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ツングースカ大爆発ってなに</v>
       </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
       <c r="K18">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L18" t="e">
+        <v>30</v>
+      </c>
+      <c r="L18">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
@@ -5529,13 +7315,34 @@
         <f>_xlfn.XLOOKUP(A19,質問シート!A:A,質問シート!C:C,"")</f>
         <v>特許を調べるサイト教えて</v>
       </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>5</v>
+      </c>
       <c r="K19">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L19" t="e">
+        <v>33</v>
+      </c>
+      <c r="L19">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
@@ -5550,13 +7357,34 @@
         <f>_xlfn.XLOOKUP(A20,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Google Patentsの使い方</v>
       </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>5</v>
+      </c>
       <c r="K20">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L20" t="e">
+        <v>32</v>
+      </c>
+      <c r="L20">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
@@ -5571,13 +7399,34 @@
         <f>_xlfn.XLOOKUP(A21,質問シート!A:A,質問シート!C:C,"")</f>
         <v>画像から場所を特定するために、最初に確認すべき情報は？</v>
       </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>5</v>
+      </c>
       <c r="K21">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L21" t="e">
+        <v>30</v>
+      </c>
+      <c r="L21">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
@@ -5592,13 +7441,34 @@
         <f>_xlfn.XLOOKUP(A22,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SNSアカウント同士の関連性を調べる一般的な方法は？</v>
       </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
       <c r="K22">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L22" t="e">
+        <v>32</v>
+      </c>
+      <c r="L22">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
@@ -5613,13 +7483,34 @@
         <f>_xlfn.XLOOKUP(A23,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ドメインの登録情報を確認するにはどんな手法がある？</v>
       </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
       <c r="K23">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L23" t="e">
+        <v>33</v>
+      </c>
+      <c r="L23">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
@@ -5634,13 +7525,34 @@
         <f>_xlfn.XLOOKUP(A24,質問シート!A:A,質問シート!C:C,"")</f>
         <v>EXIF情報から取得できる代表的なデータは？</v>
       </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
+      </c>
       <c r="K24">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L24" t="e">
+        <v>32</v>
+      </c>
+      <c r="L24">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.4">
@@ -5655,13 +7567,34 @@
         <f>_xlfn.XLOOKUP(A25,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Wayback Machineはどんな用途で使われる？</v>
       </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>5</v>
+      </c>
+      <c r="J25">
+        <v>5</v>
+      </c>
       <c r="K25">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L25" t="e">
+        <v>32</v>
+      </c>
+      <c r="L25">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
@@ -5676,13 +7609,34 @@
         <f>_xlfn.XLOOKUP(A26,質問シート!A:A,質問シート!C:C,"")</f>
         <v>GitHubの公開リポジトリから秘密情報を探す時の観点は？</v>
       </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
       <c r="K26">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L26" t="e">
+        <v>26</v>
+      </c>
+      <c r="L26">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
@@ -5697,13 +7651,34 @@
         <f>_xlfn.XLOOKUP(A27,質問シート!A:A,質問シート!C:C,"")</f>
         <v>電話番号から得られるOSINT情報には何がある？</v>
       </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
+        <v>5</v>
+      </c>
       <c r="K27">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L27" t="e">
+        <v>28</v>
+      </c>
+      <c r="L27">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.4">
@@ -5718,13 +7693,34 @@
         <f>_xlfn.XLOOKUP(A28,質問シート!A:A,質問シート!C:C,"")</f>
         <v>DNSレコードを調査すると何がわかる？</v>
       </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>5</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
       <c r="K28">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L28" t="e">
+        <v>26</v>
+      </c>
+      <c r="L28">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.4">
@@ -5739,13 +7735,34 @@
         <f>_xlfn.XLOOKUP(A29,質問シート!A:A,質問シート!C:C,"")</f>
         <v>リバースイメージサーチの代表的な使い方を教えて。</v>
       </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>5</v>
+      </c>
       <c r="K29">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L29" t="e">
+        <v>27</v>
+      </c>
+      <c r="L29">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.4">
@@ -5760,13 +7777,34 @@
         <f>_xlfn.XLOOKUP(A30,質問シート!A:A,質問シート!C:C,"")</f>
         <v>OSINTで得た情報の信頼性を検証する方法は？</v>
       </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
       <c r="K30">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L30" t="e">
+        <v>32</v>
+      </c>
+      <c r="L30">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
@@ -5781,13 +7819,34 @@
         <f>_xlfn.XLOOKUP(A31,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Webカテゴリで最初に試すべき脆弱性チェック項目を優先度順に挙げてください。</v>
       </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>4</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31">
+        <v>5</v>
+      </c>
       <c r="K31">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L31" t="e">
+        <v>28</v>
+      </c>
+      <c r="L31">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.4">
@@ -5802,13 +7861,34 @@
         <f>_xlfn.XLOOKUP(A32,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SQL Injectionの基本原理を、危険な例と安全な対策をセットで説明してください。</v>
       </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <v>4</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32">
+        <v>5</v>
+      </c>
       <c r="K32">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L32" t="e">
+        <v>24</v>
+      </c>
+      <c r="L32">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.4">
@@ -5823,13 +7903,34 @@
         <f>_xlfn.XLOOKUP(A33,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XSS（反射型・保存型・DOM型）の違いを簡潔に比較してください。</v>
       </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>5</v>
+      </c>
+      <c r="I33">
+        <v>5</v>
+      </c>
+      <c r="J33">
+        <v>5</v>
+      </c>
       <c r="K33">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L33" t="e">
+        <v>30</v>
+      </c>
+      <c r="L33">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.4">
@@ -5844,13 +7945,34 @@
         <f>_xlfn.XLOOKUP(A34,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SSRFが成立する条件と、実運用での防御策を説明してください。</v>
       </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34">
+        <v>5</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
       <c r="K34">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L34" t="e">
+        <v>28</v>
+      </c>
+      <c r="L34">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.4">
@@ -5865,13 +7987,34 @@
         <f>_xlfn.XLOOKUP(A35,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CTFのWeb問題で「ソースを見る」が有効な理由を具体例つきで説明してください。</v>
       </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>5</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
       <c r="K35">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L35" t="e">
+        <v>27</v>
+      </c>
+      <c r="L35">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.4">
@@ -5886,13 +8029,34 @@
         <f>_xlfn.XLOOKUP(A36,質問シート!A:A,質問シート!C:C,"")</f>
         <v>HTMLのコメントってどこから見れる?</v>
       </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
       <c r="K36">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L36" t="e">
+        <v>29</v>
+      </c>
+      <c r="L36">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
@@ -5907,13 +8071,34 @@
         <f>_xlfn.XLOOKUP(A37,質問シート!A:A,質問シート!C:C,"")</f>
         <v>F12を押すと何ができるの</v>
       </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <v>5</v>
+      </c>
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>5</v>
+      </c>
       <c r="K37">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L37" t="e">
+        <v>32</v>
+      </c>
+      <c r="L37">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
@@ -5928,13 +8113,34 @@
         <f>_xlfn.XLOOKUP(A38,質問シート!A:A,質問シート!C:C,"")</f>
         <v>IDORって何の略</v>
       </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>4</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
       <c r="K38">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L38" t="e">
+        <v>22</v>
+      </c>
+      <c r="L38">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.1428571428571428</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
@@ -5949,13 +8155,34 @@
         <f>_xlfn.XLOOKUP(A39,質問シート!A:A,質問シート!C:C,"")</f>
         <v>robots.txtはどんな目的で使われる？</v>
       </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>5</v>
+      </c>
+      <c r="I39">
+        <v>5</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
       <c r="K39">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L39" t="e">
+        <v>32</v>
+      </c>
+      <c r="L39">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
@@ -5970,13 +8197,34 @@
         <f>_xlfn.XLOOKUP(A40,質問シート!A:A,質問シート!C:C,"")</f>
         <v>robots.txtに書かれてる場所って入っていいの?</v>
       </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>5</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
       <c r="K40">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L40" t="e">
+        <v>30</v>
+      </c>
+      <c r="L40">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
@@ -5991,13 +8239,34 @@
         <f>_xlfn.XLOOKUP(A41,質問シート!A:A,質問シート!C:C,"")</f>
         <v>URLのid=2を1に変えたら何が起きる</v>
       </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="H41">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>5</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
       <c r="K41">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L41" t="e">
+        <v>30</v>
+      </c>
+      <c r="L41">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.4">
@@ -6012,13 +8281,34 @@
         <f>_xlfn.XLOOKUP(A42,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SQLインジェクションの基本的な仕組みを説明して。</v>
       </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42">
+        <v>4</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
       <c r="K42">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L42" t="e">
+        <v>30</v>
+      </c>
+      <c r="L42">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.4">
@@ -6033,13 +8323,34 @@
         <f>_xlfn.XLOOKUP(A43,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XSSにはどんな種類がある？</v>
       </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>4</v>
+      </c>
       <c r="K43">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L43" t="e">
+        <v>31</v>
+      </c>
+      <c r="L43">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.4">
@@ -6054,13 +8365,34 @@
         <f>_xlfn.XLOOKUP(A44,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CookieとSessionの違いは？</v>
       </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
       <c r="K44">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L44" t="e">
+        <v>32</v>
+      </c>
+      <c r="L44">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.4">
@@ -6075,13 +8407,34 @@
         <f>_xlfn.XLOOKUP(A45,質問シート!A:A,質問シート!C:C,"")</f>
         <v>HTTPレスポンスコード403と404の違いは？</v>
       </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+      <c r="J45">
+        <v>5</v>
+      </c>
       <c r="K45">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L45" t="e">
+        <v>33</v>
+      </c>
+      <c r="L45">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
@@ -6096,13 +8449,34 @@
         <f>_xlfn.XLOOKUP(A46,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Burp Suiteは何に使うツール？</v>
       </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+      <c r="H46">
+        <v>5</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
       <c r="K46">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L46" t="e">
+        <v>32</v>
+      </c>
+      <c r="L46">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.4">
@@ -6117,13 +8491,34 @@
         <f>_xlfn.XLOOKUP(A47,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CSRF攻撃はどのように成立する？</v>
       </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>4</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47">
+        <v>5</v>
+      </c>
+      <c r="J47">
+        <v>5</v>
+      </c>
       <c r="K47">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L47" t="e">
+        <v>30</v>
+      </c>
+      <c r="L47">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.4">
@@ -6138,13 +8533,34 @@
         <f>_xlfn.XLOOKUP(A48,質問シート!A:A,質問シート!C:C,"")</f>
         <v>JWTの構造を説明して。</v>
       </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>5</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="J48">
+        <v>5</v>
+      </c>
       <c r="K48">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L48" t="e">
+        <v>28</v>
+      </c>
+      <c r="L48">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.4">
@@ -6159,13 +8575,34 @@
         <f>_xlfn.XLOOKUP(A49,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ディレクトリトラバーサルとは？</v>
       </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <v>5</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+      <c r="J49">
+        <v>5</v>
+      </c>
       <c r="K49">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L49" t="e">
+        <v>30</v>
+      </c>
+      <c r="L49">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.4">
@@ -6180,13 +8617,34 @@
         <f>_xlfn.XLOOKUP(A50,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Webアプリのログインフォームを調査するときの一般的な観点は？</v>
       </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <v>4</v>
+      </c>
+      <c r="H50">
+        <v>5</v>
+      </c>
+      <c r="I50">
+        <v>5</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
       <c r="K50">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L50" t="e">
+        <v>28</v>
+      </c>
+      <c r="L50">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.4">
@@ -6201,13 +8659,34 @@
         <f>_xlfn.XLOOKUP(A51,質問シート!A:A,質問シート!C:C,"")</f>
         <v>暗号化とハッシュ化の違いを、CTFでの使い分け例つきで説明してください。</v>
       </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51">
+        <v>5</v>
+      </c>
+      <c r="I51">
+        <v>5</v>
+      </c>
+      <c r="J51">
+        <v>5</v>
+      </c>
       <c r="K51">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L51" t="e">
+        <v>31</v>
+      </c>
+      <c r="L51">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.4">
@@ -6222,13 +8701,34 @@
         <f>_xlfn.XLOOKUP(A52,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Caesar暗号とVigenere暗号の違いを、解読の観点で比較してください。</v>
       </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
+      <c r="F52">
+        <v>4</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
       <c r="K52">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L52" t="e">
+        <v>31</v>
+      </c>
+      <c r="L52">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.4">
@@ -6243,13 +8743,34 @@
         <f>_xlfn.XLOOKUP(A53,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64は暗号ですか？誤解されやすい理由も含めて説明してください。</v>
       </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>4</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+      <c r="H53">
+        <v>5</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
       <c r="K53">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L53" t="e">
+        <v>32</v>
+      </c>
+      <c r="L53">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.4">
@@ -6264,13 +8785,34 @@
         <f>_xlfn.XLOOKUP(A54,質問シート!A:A,質問シート!C:C,"")</f>
         <v>RSAの公開鍵・秘密鍵の役割を、数学が苦手な人向けに説明してください。</v>
       </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
+      <c r="G54">
+        <v>5</v>
+      </c>
+      <c r="H54">
+        <v>5</v>
+      </c>
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="J54">
+        <v>5</v>
+      </c>
       <c r="K54">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L54" t="e">
+        <v>33</v>
+      </c>
+      <c r="L54">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.4">
@@ -6285,13 +8827,34 @@
         <f>_xlfn.XLOOKUP(A55,質問シート!A:A,質問シート!C:C,"")</f>
         <v>暗号問題で「鍵長が短い」と何が起きるか、攻撃手法とあわせて説明してください。</v>
       </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
+      <c r="H55">
+        <v>5</v>
+      </c>
+      <c r="I55">
+        <v>5</v>
+      </c>
+      <c r="J55">
+        <v>5</v>
+      </c>
       <c r="K55">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L55" t="e">
+        <v>28</v>
+      </c>
+      <c r="L55">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.4">
@@ -6306,13 +8869,34 @@
         <f>_xlfn.XLOOKUP(A56,質問シート!A:A,質問シート!C:C,"")</f>
         <v>シーザー暗号ってROT13とどう違うの</v>
       </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
+        <v>3</v>
+      </c>
+      <c r="H56">
+        <v>5</v>
+      </c>
+      <c r="I56">
+        <v>5</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
       <c r="K56">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L56" t="e">
+        <v>27</v>
+      </c>
+      <c r="L56">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.4">
@@ -6327,13 +8911,34 @@
         <f>_xlfn.XLOOKUP(A57,質問シート!A:A,質問シート!C:C,"")</f>
         <v>数字をアルファベットに置き換える暗号って何ていう</v>
       </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57">
+        <v>5</v>
+      </c>
+      <c r="H57">
+        <v>5</v>
+      </c>
+      <c r="I57">
+        <v>5</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
       <c r="K57">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L57" t="e">
+        <v>31</v>
+      </c>
+      <c r="L57">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.4">
@@ -6348,13 +8953,34 @@
         <f>_xlfn.XLOOKUP(A58,質問シート!A:A,質問シート!C:C,"")</f>
         <v>A1Z26方式って聞いたことある？</v>
       </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>4</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
+      </c>
+      <c r="H58">
+        <v>5</v>
+      </c>
+      <c r="I58">
+        <v>5</v>
+      </c>
+      <c r="J58">
+        <v>5</v>
+      </c>
       <c r="K58">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L58" t="e">
+        <v>32</v>
+      </c>
+      <c r="L58">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.4">
@@ -6369,13 +8995,34 @@
         <f>_xlfn.XLOOKUP(A59,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64って何バイト単位でエンコードするの</v>
       </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>5</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
       <c r="K59">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L59" t="e">
+        <v>28</v>
+      </c>
+      <c r="L59">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.4">
@@ -6390,13 +9037,34 @@
         <f>_xlfn.XLOOKUP(A60,質問シート!A:A,質問シート!C:C,"")</f>
         <v>換字式暗号を自動で解いてくれるサイトある？</v>
       </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60">
+        <v>4</v>
+      </c>
+      <c r="F60">
+        <v>4</v>
+      </c>
+      <c r="G60">
+        <v>5</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60">
+        <v>5</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
       <c r="K60">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L60" t="e">
+        <v>32</v>
+      </c>
+      <c r="L60">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.4">
@@ -6411,13 +9079,34 @@
         <f>_xlfn.XLOOKUP(A61,質問シート!A:A,質問シート!C:C,"")</f>
         <v>quipqiupってどう使うの</v>
       </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="H61">
+        <v>5</v>
+      </c>
+      <c r="I61">
+        <v>5</v>
+      </c>
+      <c r="J61">
+        <v>4</v>
+      </c>
       <c r="K61">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L61" t="e">
+        <v>24</v>
+      </c>
+      <c r="L61">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.4">
@@ -6432,13 +9121,34 @@
         <f>_xlfn.XLOOKUP(A62,質問シート!A:A,質問シート!C:C,"")</f>
         <v>PDFのパスワードを解析する方法</v>
       </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>3</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+      <c r="I62">
+        <v>4</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
       <c r="K62">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L62" t="e">
+        <v>25</v>
+      </c>
+      <c r="L62">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.4">
@@ -6453,13 +9163,34 @@
         <f>_xlfn.XLOOKUP(A63,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ROT26で解読すればいいんですよね？</v>
       </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="H63">
+        <v>4</v>
+      </c>
+      <c r="I63">
+        <v>4</v>
+      </c>
+      <c r="J63">
+        <v>4</v>
+      </c>
       <c r="K63">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L63" t="e">
+        <v>21</v>
+      </c>
+      <c r="L63">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.4">
@@ -6474,13 +9205,34 @@
         <f>_xlfn.XLOOKUP(A64,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64って暗号だよね？</v>
       </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>5</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64">
+        <v>5</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
       <c r="K64">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L64" t="e">
+        <v>31</v>
+      </c>
+      <c r="L64">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.4">
@@ -6495,13 +9247,34 @@
         <f>_xlfn.XLOOKUP(A65,質問シート!A:A,質問シート!C:C,"")</f>
         <v>モールス信号って数字だけしか使えないの？</v>
       </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>3</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>5</v>
+      </c>
+      <c r="I65">
+        <v>5</v>
+      </c>
+      <c r="J65">
+        <v>4</v>
+      </c>
       <c r="K65">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L65" t="e">
+        <v>22</v>
+      </c>
+      <c r="L65">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.1428571428571428</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.4">
@@ -6516,13 +9289,34 @@
         <f>_xlfn.XLOOKUP(A66,質問シート!A:A,質問シート!C:C,"")</f>
         <v>john the ripperってウイルス対策ソフトでしょ？</v>
       </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+      <c r="E66">
+        <v>3</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+      <c r="G66">
+        <v>5</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66">
+        <v>5</v>
+      </c>
+      <c r="J66">
+        <v>5</v>
+      </c>
       <c r="K66">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L66" t="e">
+        <v>31</v>
+      </c>
+      <c r="L66">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.4">
@@ -6537,13 +9331,34 @@
         <f>_xlfn.XLOOKUP(A67,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ROT13とBase64って何が違うの</v>
       </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>4</v>
+      </c>
+      <c r="G67">
+        <v>4</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>5</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
       <c r="K67">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L67" t="e">
+        <v>30</v>
+      </c>
+      <c r="L67">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.4">
@@ -6558,13 +9373,34 @@
         <f>_xlfn.XLOOKUP(A68,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ステガノグラフィと暗号化って同じ？</v>
       </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>4</v>
+      </c>
+      <c r="F68">
+        <v>4</v>
+      </c>
+      <c r="G68">
+        <v>4</v>
+      </c>
+      <c r="H68">
+        <v>5</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
       <c r="K68">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L68" t="e">
+        <v>30</v>
+      </c>
+      <c r="L68">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.4">
@@ -6579,13 +9415,34 @@
         <f>_xlfn.XLOOKUP(A69,質問シート!A:A,質問シート!C:C,"")</f>
         <v>シーザー暗号の復号方法を説明して。</v>
       </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69">
+        <v>5</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>5</v>
+      </c>
+      <c r="J69">
+        <v>5</v>
+      </c>
       <c r="K69">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L69" t="e">
+        <v>33</v>
+      </c>
+      <c r="L69">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.4">
@@ -6600,13 +9457,34 @@
         <f>_xlfn.XLOOKUP(A70,質問シート!A:A,質問シート!C:C,"")</f>
         <v>共通鍵暗号と公開鍵暗号の違いは？</v>
       </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>5</v>
+      </c>
+      <c r="F70">
+        <v>4</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
+        <v>5</v>
+      </c>
       <c r="K70">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L70" t="e">
+        <v>34</v>
+      </c>
+      <c r="L70">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.4">
@@ -6621,13 +9499,34 @@
         <f>_xlfn.XLOOKUP(A71,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64は暗号なのかエンコードなのか説明して。</v>
       </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+      <c r="G71">
+        <v>5</v>
+      </c>
+      <c r="H71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>5</v>
+      </c>
+      <c r="J71">
+        <v>5</v>
+      </c>
       <c r="K71">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L71" t="e">
+        <v>31</v>
+      </c>
+      <c r="L71">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.4">
@@ -6642,13 +9541,34 @@
         <f>_xlfn.XLOOKUP(A72,質問シート!A:A,質問シート!C:C,"")</f>
         <v>RSA暗号の基本的な仕組みを教えて。</v>
       </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+      <c r="F72">
+        <v>3</v>
+      </c>
+      <c r="G72">
+        <v>4</v>
+      </c>
+      <c r="H72">
+        <v>5</v>
+      </c>
+      <c r="I72">
+        <v>5</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
       <c r="K72">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L72" t="e">
+        <v>29</v>
+      </c>
+      <c r="L72">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.4">
@@ -6663,13 +9583,34 @@
         <f>_xlfn.XLOOKUP(A73,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ハッシュ関数の用途は？</v>
       </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>4</v>
+      </c>
+      <c r="G73">
+        <v>5</v>
+      </c>
+      <c r="H73">
+        <v>5</v>
+      </c>
+      <c r="I73">
+        <v>5</v>
+      </c>
+      <c r="J73">
+        <v>5</v>
+      </c>
       <c r="K73">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L73" t="e">
+        <v>32</v>
+      </c>
+      <c r="L73">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.4">
@@ -6684,13 +9625,34 @@
         <f>_xlfn.XLOOKUP(A74,質問シート!A:A,質問シート!C:C,"")</f>
         <v>AESがよく使われる理由は？</v>
       </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>5</v>
+      </c>
+      <c r="F74">
+        <v>4</v>
+      </c>
+      <c r="G74">
+        <v>4</v>
+      </c>
+      <c r="H74">
+        <v>5</v>
+      </c>
+      <c r="I74">
+        <v>5</v>
+      </c>
+      <c r="J74">
+        <v>5</v>
+      </c>
       <c r="K74">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L74" t="e">
+        <v>33</v>
+      </c>
+      <c r="L74">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.4">
@@ -6705,13 +9667,34 @@
         <f>_xlfn.XLOOKUP(A75,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XOR暗号の特徴を説明して。</v>
       </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75">
+        <v>5</v>
+      </c>
+      <c r="I75">
+        <v>5</v>
+      </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
       <c r="K75">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L75" t="e">
+        <v>24</v>
+      </c>
+      <c r="L75">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.4">
@@ -6726,13 +9709,34 @@
         <f>_xlfn.XLOOKUP(A76,質問シート!A:A,質問シート!C:C,"")</f>
         <v>頻度分析が有効な暗号方式の例を挙げて。</v>
       </c>
+      <c r="D76">
+        <v>5</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+      <c r="F76">
+        <v>4</v>
+      </c>
+      <c r="G76">
+        <v>5</v>
+      </c>
+      <c r="H76">
+        <v>5</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
       <c r="K76">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L76" t="e">
+        <v>33</v>
+      </c>
+      <c r="L76">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.4">
@@ -6747,13 +9751,34 @@
         <f>_xlfn.XLOOKUP(A77,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ソルト付きハッシュの目的は？</v>
       </c>
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>5</v>
+      </c>
+      <c r="H77">
+        <v>5</v>
+      </c>
+      <c r="I77">
+        <v>5</v>
+      </c>
+      <c r="J77">
+        <v>5</v>
+      </c>
       <c r="K77">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L77" t="e">
+        <v>31</v>
+      </c>
+      <c r="L77">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.4">
@@ -6768,13 +9793,34 @@
         <f>_xlfn.XLOOKUP(A78,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Vigenère暗号の解読で使われる代表的な手法は？</v>
       </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>4</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78">
+        <v>4</v>
+      </c>
+      <c r="H78">
+        <v>5</v>
+      </c>
+      <c r="I78">
+        <v>5</v>
+      </c>
+      <c r="J78">
+        <v>5</v>
+      </c>
       <c r="K78">
         <f>SUM(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L78" t="e">
+        <v>32</v>
+      </c>
+      <c r="L78">
         <f>AVERAGE(テーブル13[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.4">
@@ -8817,6 +11863,28 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="D2:J175">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2.5"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L175">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -9117,13 +12185,34 @@
         <f>_xlfn.XLOOKUP(A7,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ホヌ柄の飛行機ってどこの航空会社？</v>
       </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
       <c r="K7">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L7" t="e">
+        <v>18</v>
+      </c>
+      <c r="L7">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.5714285714285716</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -9138,13 +12227,34 @@
         <f>_xlfn.XLOOKUP(A8,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ハワイの空港の公式WiFiの名前なに</v>
       </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
       <c r="K8">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L8" t="e">
+        <v>25</v>
+      </c>
+      <c r="L8">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -9159,13 +12269,34 @@
         <f>_xlfn.XLOOKUP(A9,質問シート!A:A,質問シート!C:C,"")</f>
         <v>空港のWiFiのSSIDって簡単にわかる？</v>
       </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
       <c r="K9">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L9" t="e">
+        <v>25</v>
+      </c>
+      <c r="L9">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -9180,13 +12311,34 @@
         <f>_xlfn.XLOOKUP(A10,質問シート!A:A,質問シート!C:C,"")</f>
         <v>飛行機の便名と日付って結びつけられる？</v>
       </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
       <c r="K10">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L10" t="e">
+        <v>29</v>
+      </c>
+      <c r="L10">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
@@ -9201,13 +12353,34 @@
         <f>_xlfn.XLOOKUP(A11,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ギリシャ神話で医療の神って誰</v>
       </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
       <c r="K11">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L11" t="e">
+        <v>19</v>
+      </c>
+      <c r="L11">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.7142857142857144</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
@@ -9222,13 +12395,34 @@
         <f>_xlfn.XLOOKUP(A12,質問シート!A:A,質問シート!C:C,"")</f>
         <v>杖に蛇が巻き付いてるシンボルって何の神</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
       <c r="K12">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L12" t="e">
+        <v>21</v>
+      </c>
+      <c r="L12">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -9243,13 +12437,34 @@
         <f>_xlfn.XLOOKUP(A13,質問シート!A:A,質問シート!C:C,"")</f>
         <v>創立100年くらいの有名な日本の私立大学は？</v>
       </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>5</v>
+      </c>
       <c r="K13">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L13" t="e">
+        <v>23</v>
+      </c>
+      <c r="L13">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
@@ -9264,13 +12479,34 @@
         <f>_xlfn.XLOOKUP(A14,質問シート!A:A,質問シート!C:C,"")</f>
         <v>慶應義塾を作った人って誰</v>
       </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
       <c r="K14">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L14" t="e">
+        <v>26</v>
+      </c>
+      <c r="L14">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
@@ -9285,13 +12521,34 @@
         <f>_xlfn.XLOOKUP(A15,質問シート!A:A,質問シート!C:C,"")</f>
         <v>google画像検索のやり方</v>
       </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
       <c r="K15">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L15" t="e">
+        <v>32</v>
+      </c>
+      <c r="L15">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
@@ -9306,13 +12563,34 @@
         <f>_xlfn.XLOOKUP(A16,質問シート!A:A,質問シート!C:C,"")</f>
         <v>座標から事件を調べたい</v>
       </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
       <c r="K16">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L16" t="e">
+        <v>31</v>
+      </c>
+      <c r="L16">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
@@ -9327,13 +12605,34 @@
         <f>_xlfn.XLOOKUP(A17,質問シート!A:A,質問シート!C:C,"")</f>
         <v>60.8841988,101.8857172 で何が起きた</v>
       </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
       <c r="K17">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L17" t="e">
+        <v>19</v>
+      </c>
+      <c r="L17">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.7142857142857144</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
@@ -9348,13 +12647,34 @@
         <f>_xlfn.XLOOKUP(A18,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ツングースカ大爆発ってなに</v>
       </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
       <c r="K18">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L18" t="e">
+        <v>32</v>
+      </c>
+      <c r="L18">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
@@ -9369,13 +12689,34 @@
         <f>_xlfn.XLOOKUP(A19,質問シート!A:A,質問シート!C:C,"")</f>
         <v>特許を調べるサイト教えて</v>
       </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>5</v>
+      </c>
       <c r="K19">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L19" t="e">
+        <v>34</v>
+      </c>
+      <c r="L19">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
@@ -9390,13 +12731,34 @@
         <f>_xlfn.XLOOKUP(A20,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Google Patentsの使い方</v>
       </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>5</v>
+      </c>
       <c r="K20">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L20" t="e">
+        <v>31</v>
+      </c>
+      <c r="L20">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
@@ -9411,13 +12773,34 @@
         <f>_xlfn.XLOOKUP(A21,質問シート!A:A,質問シート!C:C,"")</f>
         <v>画像から場所を特定するために、最初に確認すべき情報は？</v>
       </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>5</v>
+      </c>
       <c r="K21">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L21" t="e">
+        <v>34</v>
+      </c>
+      <c r="L21">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
@@ -9432,13 +12815,34 @@
         <f>_xlfn.XLOOKUP(A22,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SNSアカウント同士の関連性を調べる一般的な方法は？</v>
       </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
       <c r="K22">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L22" t="e">
+        <v>28</v>
+      </c>
+      <c r="L22">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
@@ -9453,13 +12857,34 @@
         <f>_xlfn.XLOOKUP(A23,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ドメインの登録情報を確認するにはどんな手法がある？</v>
       </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
       <c r="K23">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L23" t="e">
+        <v>32</v>
+      </c>
+      <c r="L23">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
@@ -9474,13 +12899,34 @@
         <f>_xlfn.XLOOKUP(A24,質問シート!A:A,質問シート!C:C,"")</f>
         <v>EXIF情報から取得できる代表的なデータは？</v>
       </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
+      </c>
       <c r="K24">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L24" t="e">
+        <v>35</v>
+      </c>
+      <c r="L24">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.4">
@@ -9495,13 +12941,34 @@
         <f>_xlfn.XLOOKUP(A25,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Wayback Machineはどんな用途で使われる？</v>
       </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>5</v>
+      </c>
+      <c r="J25">
+        <v>5</v>
+      </c>
       <c r="K25">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L25" t="e">
+        <v>34</v>
+      </c>
+      <c r="L25">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
@@ -9516,13 +12983,34 @@
         <f>_xlfn.XLOOKUP(A26,質問シート!A:A,質問シート!C:C,"")</f>
         <v>GitHubの公開リポジトリから秘密情報を探す時の観点は？</v>
       </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26">
+        <v>5</v>
+      </c>
       <c r="K26">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L26" t="e">
+        <v>30</v>
+      </c>
+      <c r="L26">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
@@ -9537,13 +13025,34 @@
         <f>_xlfn.XLOOKUP(A27,質問シート!A:A,質問シート!C:C,"")</f>
         <v>電話番号から得られるOSINT情報には何がある？</v>
       </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
+      </c>
+      <c r="J27">
+        <v>5</v>
+      </c>
       <c r="K27">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L27" t="e">
+        <v>26</v>
+      </c>
+      <c r="L27">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.7142857142857144</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.4">
@@ -9558,13 +13067,34 @@
         <f>_xlfn.XLOOKUP(A28,質問シート!A:A,質問シート!C:C,"")</f>
         <v>DNSレコードを調査すると何がわかる？</v>
       </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
       <c r="K28">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L28" t="e">
+        <v>32</v>
+      </c>
+      <c r="L28">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.4">
@@ -9579,13 +13109,34 @@
         <f>_xlfn.XLOOKUP(A29,質問シート!A:A,質問シート!C:C,"")</f>
         <v>リバースイメージサーチの代表的な使い方を教えて。</v>
       </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>5</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29">
+        <v>5</v>
+      </c>
       <c r="K29">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L29" t="e">
+        <v>31</v>
+      </c>
+      <c r="L29">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.4">
@@ -9600,13 +13151,34 @@
         <f>_xlfn.XLOOKUP(A30,質問シート!A:A,質問シート!C:C,"")</f>
         <v>OSINTで得た情報の信頼性を検証する方法は？</v>
       </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
       <c r="K30">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L30" t="e">
+        <v>34</v>
+      </c>
+      <c r="L30">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
@@ -9621,13 +13193,34 @@
         <f>_xlfn.XLOOKUP(A31,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Webカテゴリで最初に試すべき脆弱性チェック項目を優先度順に挙げてください。</v>
       </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>4</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31">
+        <v>5</v>
+      </c>
       <c r="K31">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L31" t="e">
+        <v>30</v>
+      </c>
+      <c r="L31">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.4">
@@ -9642,13 +13235,34 @@
         <f>_xlfn.XLOOKUP(A32,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SQL Injectionの基本原理を、危険な例と安全な対策をセットで説明してください。</v>
       </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>4</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32">
+        <v>5</v>
+      </c>
       <c r="K32">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L32" t="e">
+        <v>32</v>
+      </c>
+      <c r="L32">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.4">
@@ -9663,13 +13277,34 @@
         <f>_xlfn.XLOOKUP(A33,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XSS（反射型・保存型・DOM型）の違いを簡潔に比較してください。</v>
       </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>5</v>
+      </c>
+      <c r="I33">
+        <v>5</v>
+      </c>
+      <c r="J33">
+        <v>5</v>
+      </c>
       <c r="K33">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L33" t="e">
+        <v>35</v>
+      </c>
+      <c r="L33">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.4">
@@ -9684,13 +13319,34 @@
         <f>_xlfn.XLOOKUP(A34,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SSRFが成立する条件と、実運用での防御策を説明してください。</v>
       </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34">
+        <v>5</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
       <c r="K34">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L34" t="e">
+        <v>33</v>
+      </c>
+      <c r="L34">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.4">
@@ -9705,13 +13361,34 @@
         <f>_xlfn.XLOOKUP(A35,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CTFのWeb問題で「ソースを見る」が有効な理由を具体例つきで説明してください。</v>
       </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
       <c r="K35">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L35" t="e">
+        <v>19</v>
+      </c>
+      <c r="L35">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.7142857142857144</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.4">
@@ -9726,13 +13403,34 @@
         <f>_xlfn.XLOOKUP(A36,質問シート!A:A,質問シート!C:C,"")</f>
         <v>HTMLのコメントってどこから見れる?</v>
       </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
       <c r="K36">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L36" t="e">
+        <v>32</v>
+      </c>
+      <c r="L36">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
@@ -9747,13 +13445,34 @@
         <f>_xlfn.XLOOKUP(A37,質問シート!A:A,質問シート!C:C,"")</f>
         <v>F12を押すと何ができるの</v>
       </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <v>5</v>
+      </c>
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
       <c r="K37">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L37" t="e">
+        <v>29</v>
+      </c>
+      <c r="L37">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
@@ -9768,13 +13487,34 @@
         <f>_xlfn.XLOOKUP(A38,質問シート!A:A,質問シート!C:C,"")</f>
         <v>IDORって何の略</v>
       </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>5</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
       <c r="K38">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L38" t="e">
+        <v>33</v>
+      </c>
+      <c r="L38">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
@@ -9789,13 +13529,34 @@
         <f>_xlfn.XLOOKUP(A39,質問シート!A:A,質問シート!C:C,"")</f>
         <v>robots.txtはどんな目的で使われる？</v>
       </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
       <c r="K39">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L39" t="e">
+        <v>28</v>
+      </c>
+      <c r="L39">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
@@ -9810,13 +13571,34 @@
         <f>_xlfn.XLOOKUP(A40,質問シート!A:A,質問シート!C:C,"")</f>
         <v>robots.txtに書かれてる場所って入っていいの?</v>
       </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
       <c r="K40">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L40" t="e">
+        <v>31</v>
+      </c>
+      <c r="L40">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
@@ -9831,13 +13613,34 @@
         <f>_xlfn.XLOOKUP(A41,質問シート!A:A,質問シート!C:C,"")</f>
         <v>URLのid=2を1に変えたら何が起きる</v>
       </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
       <c r="K41">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L41" t="e">
+        <v>20</v>
+      </c>
+      <c r="L41">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.8571428571428572</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.4">
@@ -9852,13 +13655,34 @@
         <f>_xlfn.XLOOKUP(A42,質問シート!A:A,質問シート!C:C,"")</f>
         <v>SQLインジェクションの基本的な仕組みを説明して。</v>
       </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>4</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
       <c r="K42">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L42" t="e">
+        <v>31</v>
+      </c>
+      <c r="L42">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.4">
@@ -9873,13 +13697,34 @@
         <f>_xlfn.XLOOKUP(A43,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XSSにはどんな種類がある？</v>
       </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
       <c r="K43">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L43" t="e">
+        <v>25</v>
+      </c>
+      <c r="L43">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.4">
@@ -9894,13 +13739,34 @@
         <f>_xlfn.XLOOKUP(A44,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CookieとSessionの違いは？</v>
       </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <v>4</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>4</v>
+      </c>
       <c r="K44">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L44" t="e">
+        <v>33</v>
+      </c>
+      <c r="L44">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.4">
@@ -9915,13 +13781,34 @@
         <f>_xlfn.XLOOKUP(A45,質問シート!A:A,質問シート!C:C,"")</f>
         <v>HTTPレスポンスコード403と404の違いは？</v>
       </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45">
+        <v>4</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+      <c r="J45">
+        <v>5</v>
+      </c>
       <c r="K45">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L45" t="e">
+        <v>34</v>
+      </c>
+      <c r="L45">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
@@ -9936,13 +13823,34 @@
         <f>_xlfn.XLOOKUP(A46,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Burp Suiteは何に使うツール？</v>
       </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>5</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
       <c r="K46">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L46" t="e">
+        <v>32</v>
+      </c>
+      <c r="L46">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.4">
@@ -9957,13 +13865,34 @@
         <f>_xlfn.XLOOKUP(A47,質問シート!A:A,質問シート!C:C,"")</f>
         <v>CSRF攻撃はどのように成立する？</v>
       </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>4</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47">
+        <v>5</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
       <c r="K47">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L47" t="e">
+        <v>30</v>
+      </c>
+      <c r="L47">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.4">
@@ -9978,13 +13907,34 @@
         <f>_xlfn.XLOOKUP(A48,質問シート!A:A,質問シート!C:C,"")</f>
         <v>JWTの構造を説明して。</v>
       </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48">
+        <v>5</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
       <c r="K48">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L48" t="e">
+        <v>33</v>
+      </c>
+      <c r="L48">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.4">
@@ -9999,13 +13949,34 @@
         <f>_xlfn.XLOOKUP(A49,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ディレクトリトラバーサルとは？</v>
       </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+      <c r="J49">
+        <v>5</v>
+      </c>
       <c r="K49">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L49" t="e">
+        <v>33</v>
+      </c>
+      <c r="L49">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.4">
@@ -10020,13 +13991,34 @@
         <f>_xlfn.XLOOKUP(A50,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Webアプリのログインフォームを調査するときの一般的な観点は？</v>
       </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>4</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50">
+        <v>4</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
       <c r="K50">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L50" t="e">
+        <v>31</v>
+      </c>
+      <c r="L50">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.4">
@@ -10041,13 +14033,34 @@
         <f>_xlfn.XLOOKUP(A51,質問シート!A:A,質問シート!C:C,"")</f>
         <v>暗号化とハッシュ化の違いを、CTFでの使い分け例つきで説明してください。</v>
       </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51">
+        <v>5</v>
+      </c>
+      <c r="I51">
+        <v>5</v>
+      </c>
+      <c r="J51">
+        <v>5</v>
+      </c>
       <c r="K51">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L51" t="e">
+        <v>32</v>
+      </c>
+      <c r="L51">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.4">
@@ -10062,13 +14075,34 @@
         <f>_xlfn.XLOOKUP(A52,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Caesar暗号とVigenere暗号の違いを、解読の観点で比較してください。</v>
       </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52">
+        <v>5</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
       <c r="K52">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L52" t="e">
+        <v>33</v>
+      </c>
+      <c r="L52">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.4">
@@ -10083,13 +14117,34 @@
         <f>_xlfn.XLOOKUP(A53,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64は暗号ですか？誤解されやすい理由も含めて説明してください。</v>
       </c>
+      <c r="D53">
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+      <c r="H53">
+        <v>5</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
       <c r="K53">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L53" t="e">
+        <v>35</v>
+      </c>
+      <c r="L53">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.4">
@@ -10104,13 +14159,34 @@
         <f>_xlfn.XLOOKUP(A54,質問シート!A:A,質問シート!C:C,"")</f>
         <v>RSAの公開鍵・秘密鍵の役割を、数学が苦手な人向けに説明してください。</v>
       </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>5</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="H54">
+        <v>5</v>
+      </c>
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="J54">
+        <v>4</v>
+      </c>
       <c r="K54">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L54" t="e">
+        <v>29</v>
+      </c>
+      <c r="L54">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.4">
@@ -10125,13 +14201,34 @@
         <f>_xlfn.XLOOKUP(A55,質問シート!A:A,質問シート!C:C,"")</f>
         <v>暗号問題で「鍵長が短い」と何が起きるか、攻撃手法とあわせて説明してください。</v>
       </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55">
+        <v>4</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55">
+        <v>5</v>
+      </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
       <c r="K55">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L55" t="e">
+        <v>31</v>
+      </c>
+      <c r="L55">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.4">
@@ -10146,13 +14243,34 @@
         <f>_xlfn.XLOOKUP(A56,質問シート!A:A,質問シート!C:C,"")</f>
         <v>シーザー暗号ってROT13とどう違うの</v>
       </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+      <c r="H56">
+        <v>5</v>
+      </c>
+      <c r="I56">
+        <v>5</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
       <c r="K56">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L56" t="e">
+        <v>34</v>
+      </c>
+      <c r="L56">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.4">
@@ -10167,13 +14285,34 @@
         <f>_xlfn.XLOOKUP(A57,質問シート!A:A,質問シート!C:C,"")</f>
         <v>数字をアルファベットに置き換える暗号って何ていう</v>
       </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57">
+        <v>4</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57">
+        <v>5</v>
+      </c>
+      <c r="H57">
+        <v>5</v>
+      </c>
+      <c r="I57">
+        <v>5</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
       <c r="K57">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L57" t="e">
+        <v>33</v>
+      </c>
+      <c r="L57">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.4">
@@ -10188,13 +14327,34 @@
         <f>_xlfn.XLOOKUP(A58,質問シート!A:A,質問シート!C:C,"")</f>
         <v>A1Z26方式って聞いたことある？</v>
       </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
+      </c>
+      <c r="H58">
+        <v>5</v>
+      </c>
+      <c r="I58">
+        <v>5</v>
+      </c>
+      <c r="J58">
+        <v>5</v>
+      </c>
       <c r="K58">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L58" t="e">
+        <v>35</v>
+      </c>
+      <c r="L58">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.4">
@@ -10209,13 +14369,34 @@
         <f>_xlfn.XLOOKUP(A59,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64って何バイト単位でエンコードするの</v>
       </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>3</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="H59">
+        <v>5</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
       <c r="K59">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L59" t="e">
+        <v>23</v>
+      </c>
+      <c r="L59">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.4">
@@ -10230,13 +14411,34 @@
         <f>_xlfn.XLOOKUP(A60,質問シート!A:A,質問シート!C:C,"")</f>
         <v>換字式暗号を自動で解いてくれるサイトある？</v>
       </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60">
+        <v>4</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60">
+        <v>5</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60">
+        <v>5</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
       <c r="K60">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L60" t="e">
+        <v>33</v>
+      </c>
+      <c r="L60">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.4">
@@ -10251,13 +14453,34 @@
         <f>_xlfn.XLOOKUP(A61,質問シート!A:A,質問シート!C:C,"")</f>
         <v>quipqiupってどう使うの</v>
       </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>5</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61">
+        <v>5</v>
+      </c>
       <c r="K61">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L61" t="e">
+        <v>20</v>
+      </c>
+      <c r="L61">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.8571428571428572</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.4">
@@ -10272,13 +14495,34 @@
         <f>_xlfn.XLOOKUP(A62,質問シート!A:A,質問シート!C:C,"")</f>
         <v>PDFのパスワードを解析する方法</v>
       </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>3</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>3</v>
+      </c>
+      <c r="H62">
+        <v>4</v>
+      </c>
+      <c r="I62">
+        <v>4</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
       <c r="K62">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L62" t="e">
+        <v>24</v>
+      </c>
+      <c r="L62">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.4285714285714284</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.4">
@@ -10293,13 +14537,34 @@
         <f>_xlfn.XLOOKUP(A63,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ROT26で解読すればいいんですよね？</v>
       </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>5</v>
+      </c>
+      <c r="I63">
+        <v>5</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
       <c r="K63">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L63" t="e">
+        <v>17</v>
+      </c>
+      <c r="L63">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>2.4285714285714284</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.4">
@@ -10314,13 +14579,34 @@
         <f>_xlfn.XLOOKUP(A64,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64って暗号だよね？</v>
       </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>5</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64">
+        <v>5</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
+      </c>
       <c r="K64">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L64" t="e">
+        <v>32</v>
+      </c>
+      <c r="L64">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.4">
@@ -10335,13 +14621,34 @@
         <f>_xlfn.XLOOKUP(A65,質問シート!A:A,質問シート!C:C,"")</f>
         <v>モールス信号って数字だけしか使えないの？</v>
       </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
+        <v>5</v>
+      </c>
+      <c r="H65">
+        <v>5</v>
+      </c>
+      <c r="I65">
+        <v>5</v>
+      </c>
+      <c r="J65">
+        <v>5</v>
+      </c>
       <c r="K65">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L65" t="e">
+        <v>34</v>
+      </c>
+      <c r="L65">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.8571428571428568</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.4">
@@ -10356,13 +14663,34 @@
         <f>_xlfn.XLOOKUP(A66,質問シート!A:A,質問シート!C:C,"")</f>
         <v>john the ripperってウイルス対策ソフトでしょ？</v>
       </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+      <c r="E66">
+        <v>4</v>
+      </c>
+      <c r="F66">
+        <v>4</v>
+      </c>
+      <c r="G66">
+        <v>4</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66">
+        <v>5</v>
+      </c>
+      <c r="J66">
+        <v>5</v>
+      </c>
       <c r="K66">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L66" t="e">
+        <v>32</v>
+      </c>
+      <c r="L66">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.4">
@@ -10377,13 +14705,34 @@
         <f>_xlfn.XLOOKUP(A67,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ROT13とBase64って何が違うの</v>
       </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>5</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+      <c r="G67">
+        <v>4</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>5</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
       <c r="K67">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L67" t="e">
+        <v>32</v>
+      </c>
+      <c r="L67">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.4">
@@ -10398,13 +14747,34 @@
         <f>_xlfn.XLOOKUP(A68,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ステガノグラフィと暗号化って同じ？</v>
       </c>
+      <c r="D68">
+        <v>2</v>
+      </c>
+      <c r="E68">
+        <v>4</v>
+      </c>
+      <c r="F68">
+        <v>4</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68">
+        <v>4</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
       <c r="K68">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L68" t="e">
+        <v>27</v>
+      </c>
+      <c r="L68">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.4">
@@ -10419,13 +14789,34 @@
         <f>_xlfn.XLOOKUP(A69,質問シート!A:A,質問シート!C:C,"")</f>
         <v>シーザー暗号の復号方法を説明して。</v>
       </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69">
+        <v>4</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>5</v>
+      </c>
+      <c r="J69">
+        <v>5</v>
+      </c>
       <c r="K69">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L69" t="e">
+        <v>30</v>
+      </c>
+      <c r="L69">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.4">
@@ -10440,13 +14831,34 @@
         <f>_xlfn.XLOOKUP(A70,質問シート!A:A,質問シート!C:C,"")</f>
         <v>共通鍵暗号と公開鍵暗号の違いは？</v>
       </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70">
+        <v>4</v>
+      </c>
+      <c r="F70">
+        <v>4</v>
+      </c>
+      <c r="G70">
+        <v>4</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
+        <v>5</v>
+      </c>
       <c r="K70">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L70" t="e">
+        <v>31</v>
+      </c>
+      <c r="L70">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.4">
@@ -10461,13 +14873,34 @@
         <f>_xlfn.XLOOKUP(A71,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Base64は暗号なのかエンコードなのか説明して。</v>
       </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71">
+        <v>4</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>5</v>
+      </c>
+      <c r="J71">
+        <v>5</v>
+      </c>
       <c r="K71">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L71" t="e">
+        <v>31</v>
+      </c>
+      <c r="L71">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.4285714285714288</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.4">
@@ -10482,13 +14915,34 @@
         <f>_xlfn.XLOOKUP(A72,質問シート!A:A,質問シート!C:C,"")</f>
         <v>RSA暗号の基本的な仕組みを教えて。</v>
       </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+      <c r="F72">
+        <v>4</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+      <c r="H72">
+        <v>5</v>
+      </c>
+      <c r="I72">
+        <v>5</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
       <c r="K72">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L72" t="e">
+        <v>29</v>
+      </c>
+      <c r="L72">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.4">
@@ -10503,13 +14957,34 @@
         <f>_xlfn.XLOOKUP(A73,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ハッシュ関数の用途は？</v>
       </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>5</v>
+      </c>
+      <c r="F73">
+        <v>5</v>
+      </c>
+      <c r="G73">
+        <v>4</v>
+      </c>
+      <c r="H73">
+        <v>5</v>
+      </c>
+      <c r="I73">
+        <v>5</v>
+      </c>
+      <c r="J73">
+        <v>5</v>
+      </c>
       <c r="K73">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L73" t="e">
+        <v>33</v>
+      </c>
+      <c r="L73">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.7142857142857144</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.4">
@@ -10524,13 +14999,34 @@
         <f>_xlfn.XLOOKUP(A74,質問シート!A:A,質問シート!C:C,"")</f>
         <v>AESがよく使われる理由は？</v>
       </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+      <c r="F74">
+        <v>4</v>
+      </c>
+      <c r="G74">
+        <v>4</v>
+      </c>
+      <c r="H74">
+        <v>5</v>
+      </c>
+      <c r="I74">
+        <v>5</v>
+      </c>
+      <c r="J74">
+        <v>5</v>
+      </c>
       <c r="K74">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L74" t="e">
+        <v>32</v>
+      </c>
+      <c r="L74">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4.5714285714285712</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.4">
@@ -10545,13 +15041,34 @@
         <f>_xlfn.XLOOKUP(A75,質問シート!A:A,質問シート!C:C,"")</f>
         <v>XOR暗号の特徴を説明して。</v>
       </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <v>3</v>
+      </c>
+      <c r="H75">
+        <v>4</v>
+      </c>
+      <c r="I75">
+        <v>4</v>
+      </c>
+      <c r="J75">
+        <v>4</v>
+      </c>
       <c r="K75">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L75" t="e">
+        <v>25</v>
+      </c>
+      <c r="L75">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.5714285714285716</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.4">
@@ -10566,13 +15083,34 @@
         <f>_xlfn.XLOOKUP(A76,質問シート!A:A,質問シート!C:C,"")</f>
         <v>頻度分析が有効な暗号方式の例を挙げて。</v>
       </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+      <c r="H76">
+        <v>5</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
       <c r="K76">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L76" t="e">
+        <v>27</v>
+      </c>
+      <c r="L76">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.4">
@@ -10587,13 +15125,34 @@
         <f>_xlfn.XLOOKUP(A77,質問シート!A:A,質問シート!C:C,"")</f>
         <v>ソルト付きハッシュの目的は？</v>
       </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>3</v>
+      </c>
+      <c r="H77">
+        <v>5</v>
+      </c>
+      <c r="I77">
+        <v>5</v>
+      </c>
+      <c r="J77">
+        <v>5</v>
+      </c>
       <c r="K77">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L77" t="e">
+        <v>28</v>
+      </c>
+      <c r="L77">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.4">
@@ -10608,13 +15167,34 @@
         <f>_xlfn.XLOOKUP(A78,質問シート!A:A,質問シート!C:C,"")</f>
         <v>Vigenère暗号の解読で使われる代表的な手法は？</v>
       </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="E78">
+        <v>4</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
+      <c r="H78">
+        <v>5</v>
+      </c>
+      <c r="I78">
+        <v>5</v>
+      </c>
+      <c r="J78">
+        <v>5</v>
+      </c>
       <c r="K78">
         <f>SUM(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>0</v>
-      </c>
-      <c r="L78" t="e">
+        <v>27</v>
+      </c>
+      <c r="L78">
         <f>AVERAGE(テーブル134[[#This Row],[正確性]:[日本語の自然さ]])</f>
-        <v>#DIV/0!</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.4">
@@ -12657,6 +17237,28 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="D2:J175">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2.5"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L175">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="1"/>
